--- a/artfynd/A 28667-2025 artfynd.xlsx
+++ b/artfynd/A 28667-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>130174014</v>
       </c>
       <c r="B3" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28667-2025 artfynd.xlsx
+++ b/artfynd/A 28667-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>130174014</v>
       </c>
       <c r="B3" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28667-2025 artfynd.xlsx
+++ b/artfynd/A 28667-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>130174014</v>
       </c>
       <c r="B3" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28667-2025 artfynd.xlsx
+++ b/artfynd/A 28667-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124758546</v>
+        <v>132712698</v>
       </c>
       <c r="B2" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Muskboberget, Dlr</t>
+          <t>Åkersmyra, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516614</v>
+        <v>516520</v>
       </c>
       <c r="R2" t="n">
-        <v>6706388</v>
+        <v>6706339</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -753,12 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fruktkroppar från hösten 2025.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130174014</v>
+        <v>132712683</v>
       </c>
       <c r="B3" t="n">
-        <v>57044</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,23 +822,23 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åkersmyra Fäbodar, Dlr</t>
+          <t>Åkersmyra, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516476</v>
+        <v>516524</v>
       </c>
       <c r="R3" t="n">
-        <v>6706363</v>
+        <v>6706355</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,12 +862,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack nedtill tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132420211</v>
+        <v>130173526</v>
       </c>
       <c r="B4" t="n">
-        <v>57145</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,20 +932,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åkersmyra Fäbod, Dlr</t>
+          <t>Åkersmyra Fäbodar, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516483</v>
+        <v>516615</v>
       </c>
       <c r="R4" t="n">
-        <v>6706367</v>
+        <v>6706420</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -963,12 +972,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132712698</v>
+        <v>124758546</v>
       </c>
       <c r="B5" t="n">
-        <v>93206</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,45 +1020,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åkersmyra, Dlr</t>
+          <t>Muskboberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516520</v>
+        <v>516614</v>
       </c>
       <c r="R5" t="n">
-        <v>6706339</v>
+        <v>6706388</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1071,17 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fruktkroppar från hösten 2025.</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,7 +1096,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1109,32 +1114,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132712683</v>
+        <v>130174014</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,23 +1147,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åkersmyra, Dlr</t>
+          <t>Åkersmyra Fäbodar, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516524</v>
+        <v>516476</v>
       </c>
       <c r="R6" t="n">
-        <v>6706355</v>
+        <v>6706363</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,17 +1187,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack nedtill tall.</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,6 +1216,111 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132420211</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åkersmyra Fäbod, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>516483</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6706367</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28667-2025 artfynd.xlsx
+++ b/artfynd/A 28667-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132712698</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132712683</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130173526</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124758546</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130174014</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,8 +1351,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132420211</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>